--- a/backtest_runs/20260410_193731/by_symbol/EPCLPS/EPCLPS.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/EPCLPS/EPCLPS.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -587,7 +587,7 @@
         <v>-1138.200000000005</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" s="2" t="n">
         <v>98861.79999999999</v>
@@ -909,7 +909,7 @@
         <v>-487.800000000004</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>99512.2</v>
@@ -952,10 +952,10 @@
         </is>
       </c>
       <c r="I11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K11" s="3" t="n">
         <v>99512.2</v>
@@ -1044,10 +1044,10 @@
         </is>
       </c>
       <c r="I13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="3" t="n">
         <v>100731.7</v>
@@ -1093,7 +1093,7 @@
         <v>-8048.700000000002</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K14" s="2" t="n">
         <v>92683</v>
@@ -1185,7 +1185,7 @@
         <v>-487.800000000004</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>92195.2</v>
@@ -1461,7 +1461,7 @@
         <v>-406.5000000000058</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>91788.69999999998</v>
